--- a/Cardiologie/Excel/cardio_14.xlsx
+++ b/Cardiologie/Excel/cardio_14.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moito\Desktop\Sérieux\Projet\Site web\Cardiologie\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74FC2443-C544-48F3-A85B-9DBCD1D2822D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7F56317-9B7E-48DA-A1E6-2A49215CAF8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,16 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="205">
-  <si>
-    <t>numero</t>
-  </si>
-  <si>
-    <t>proposition</t>
-  </si>
-  <si>
-    <t>reponse</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="207">
   <si>
     <t>Le réseau veineux des membres inférieurs comprend un réseau superficiel et un réseau profond.</t>
   </si>
@@ -631,26 +622,33 @@
     <t>Les stations debout et assise prolongées sont à éviter dans la mesure du possible en cas de varices.</t>
   </si>
   <si>
-    <t>Vrai</t>
-  </si>
-  <si>
-    <t>Faux</t>
+    <t>Numero</t>
+  </si>
+  <si>
+    <t>Proposition</t>
+  </si>
+  <si>
+    <t>Reponse</t>
+  </si>
+  <si>
+    <t>Justification</t>
+  </si>
+  <si>
+    <t>Reference</t>
+  </si>
+  <si>
+    <t>Question</t>
+  </si>
+  <si>
+    <t>image</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -666,27 +664,12 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -695,11 +678,11 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1005,2224 +988,2236 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C201"/>
+  <dimension ref="A1:G201"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="186.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="186.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+    <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
+      <c r="B3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
+      <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C4" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
+      <c r="B5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C5" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
+      <c r="B6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C6" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
+      <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C7" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
+      <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C8" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
+      <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C9" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
+      <c r="B10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C10" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
+      <c r="B11" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C11" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
+      <c r="B12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C12" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
         <v>12</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
+      <c r="B13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="C13" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
         <v>13</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="2">
+      <c r="B14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="C14" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
         <v>14</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="2">
+      <c r="B15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C15" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
         <v>15</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="2">
+      <c r="B16" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="C16" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
         <v>16</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="2">
+      <c r="B17" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="C17" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
         <v>17</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="2">
+      <c r="B18" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="C18" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
         <v>18</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="2">
+      <c r="B19" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="C19" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
         <v>19</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="2">
+      <c r="B20" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="C20" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
         <v>20</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="2">
+      <c r="B21" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="C21" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
         <v>21</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="2">
+      <c r="B22" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="C22" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
         <v>22</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="2">
+      <c r="B23" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="C23" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
         <v>23</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="2">
+      <c r="B24" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="C24" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
         <v>24</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="2">
+      <c r="B25" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="C25" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
         <v>25</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="2">
+      <c r="B26" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="C26" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
         <v>26</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="2">
+      <c r="B27" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="C27" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
         <v>27</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="2">
+      <c r="B28" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="C28" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
         <v>28</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="2">
+      <c r="B29" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="C29" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
         <v>29</v>
       </c>
-      <c r="C28" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="2">
+      <c r="B30" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="C30" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
         <v>30</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="2">
+      <c r="B31" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="C31" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
         <v>31</v>
       </c>
-      <c r="C30" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="2">
+      <c r="B32" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="C32" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
         <v>32</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="2">
+      <c r="B33" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="C33" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
         <v>33</v>
       </c>
-      <c r="C32" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="2">
+      <c r="B34" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="C34" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
         <v>34</v>
       </c>
-      <c r="C33" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="2">
+      <c r="B35" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="C35" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
         <v>35</v>
       </c>
-      <c r="C34" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="2">
+      <c r="B36" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="C36" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
         <v>36</v>
       </c>
-      <c r="C35" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="2">
+      <c r="B37" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="C37" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
         <v>37</v>
       </c>
-      <c r="C36" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="2">
+      <c r="B38" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="C38" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
         <v>38</v>
       </c>
-      <c r="C37" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="2">
+      <c r="B39" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="C39" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
         <v>39</v>
       </c>
-      <c r="C38" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="2">
+      <c r="B40" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="C40" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
         <v>40</v>
       </c>
-      <c r="C39" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="2">
+      <c r="B41" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="C41" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
         <v>41</v>
       </c>
-      <c r="C40" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="2">
+      <c r="B42" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="C42" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
         <v>42</v>
       </c>
-      <c r="C41" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="2">
+      <c r="B43" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="C43" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="1">
         <v>43</v>
       </c>
-      <c r="C42" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="2">
+      <c r="B44" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="C44" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
         <v>44</v>
       </c>
-      <c r="C43" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="2">
+      <c r="B45" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="C45" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
         <v>45</v>
       </c>
-      <c r="C44" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="2">
+      <c r="B46" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="C46" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
         <v>46</v>
       </c>
-      <c r="C45" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="2">
+      <c r="B47" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="C47" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
         <v>47</v>
       </c>
-      <c r="C46" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="2">
+      <c r="B48" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="C48" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
         <v>48</v>
       </c>
-      <c r="C47" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="2">
+      <c r="B49" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="C49" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
         <v>49</v>
       </c>
-      <c r="C48" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="2">
+      <c r="B50" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="C50" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
         <v>50</v>
       </c>
-      <c r="C49" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="2">
+      <c r="B51" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="C51" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
         <v>51</v>
       </c>
-      <c r="C50" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="2">
+      <c r="B52" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="C52" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
         <v>52</v>
       </c>
-      <c r="C51" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="2">
+      <c r="B53" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="C53" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="1">
         <v>53</v>
       </c>
-      <c r="C52" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="2">
+      <c r="B54" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="C54" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="1">
         <v>54</v>
       </c>
-      <c r="C53" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="2">
+      <c r="B55" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="C55" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="1">
         <v>55</v>
       </c>
-      <c r="C54" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="2">
+      <c r="B56" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="C56" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="1">
         <v>56</v>
       </c>
-      <c r="C55" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="2">
+      <c r="B57" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="C57" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="1">
         <v>57</v>
       </c>
-      <c r="C56" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="2">
+      <c r="B58" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="C58" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="1">
         <v>58</v>
       </c>
-      <c r="C57" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="2">
+      <c r="B59" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="C59" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="1">
         <v>59</v>
       </c>
-      <c r="C58" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="2">
+      <c r="B60" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="C60" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="1">
         <v>60</v>
       </c>
-      <c r="C59" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="2">
+      <c r="B61" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="C61" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="1">
         <v>61</v>
       </c>
-      <c r="C60" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="2">
+      <c r="B62" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B61" s="2" t="s">
+      <c r="C62" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="1">
         <v>62</v>
       </c>
-      <c r="C61" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="2">
+      <c r="B63" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="C63" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="1">
         <v>63</v>
       </c>
-      <c r="C62" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="2">
+      <c r="B64" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B63" s="2" t="s">
+      <c r="C64" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="1">
         <v>64</v>
       </c>
-      <c r="C63" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="2">
+      <c r="B65" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B64" s="2" t="s">
+      <c r="C65" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="1">
         <v>65</v>
       </c>
-      <c r="C64" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="2">
+      <c r="B66" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B65" s="2" t="s">
+      <c r="C66" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="1">
         <v>66</v>
       </c>
-      <c r="C65" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="2">
+      <c r="B67" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B66" s="2" t="s">
+      <c r="C67" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="1">
         <v>67</v>
       </c>
-      <c r="C66" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="2">
+      <c r="B68" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B67" s="2" t="s">
+      <c r="C68" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="1">
         <v>68</v>
       </c>
-      <c r="C67" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="2">
+      <c r="B69" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B68" s="2" t="s">
+      <c r="C69" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="1">
         <v>69</v>
       </c>
-      <c r="C68" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" s="2">
+      <c r="B70" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B69" s="2" t="s">
+      <c r="C70" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="1">
         <v>70</v>
       </c>
-      <c r="C69" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" s="2">
+      <c r="B71" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B70" s="2" t="s">
+      <c r="C71" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="1">
         <v>71</v>
       </c>
-      <c r="C70" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" s="2">
+      <c r="B72" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B71" s="2" t="s">
+      <c r="C72" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="1">
         <v>72</v>
       </c>
-      <c r="C71" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" s="2">
+      <c r="B73" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B72" s="2" t="s">
+      <c r="C73" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="1">
         <v>73</v>
       </c>
-      <c r="C72" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" s="2">
+      <c r="B74" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B73" s="2" t="s">
+      <c r="C74" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="1">
         <v>74</v>
       </c>
-      <c r="C73" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" s="2">
+      <c r="B75" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B74" s="2" t="s">
+      <c r="C75" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="1">
         <v>75</v>
       </c>
-      <c r="C74" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" s="2">
+      <c r="B76" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B75" s="2" t="s">
+      <c r="C76" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="1">
         <v>76</v>
       </c>
-      <c r="C75" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" s="2">
+      <c r="B77" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B76" s="2" t="s">
+      <c r="C77" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="1">
         <v>77</v>
       </c>
-      <c r="C76" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" s="2">
+      <c r="B78" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B77" s="2" t="s">
+      <c r="C78" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="1">
         <v>78</v>
       </c>
-      <c r="C77" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" s="2">
+      <c r="B79" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B78" s="2" t="s">
+      <c r="C79" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="1">
         <v>79</v>
       </c>
-      <c r="C78" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" s="2">
+      <c r="B80" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B79" s="2" t="s">
+      <c r="C80" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="1">
         <v>80</v>
       </c>
-      <c r="C79" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" s="2">
+      <c r="B81" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B80" s="2" t="s">
+      <c r="C81" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="1">
         <v>81</v>
       </c>
-      <c r="C80" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="2">
+      <c r="B82" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B81" s="2" t="s">
+      <c r="C82" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="1">
         <v>82</v>
       </c>
-      <c r="C81" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" s="2">
+      <c r="B83" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B82" s="2" t="s">
+      <c r="C83" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="1">
         <v>83</v>
       </c>
-      <c r="C82" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" s="2">
+      <c r="B84" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B83" s="2" t="s">
+      <c r="C84" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="1">
         <v>84</v>
       </c>
-      <c r="C83" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" s="2">
+      <c r="B85" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B84" s="2" t="s">
+      <c r="C85" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="1">
         <v>85</v>
       </c>
-      <c r="C84" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" s="2">
+      <c r="B86" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B85" s="2" t="s">
+      <c r="C86" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="1">
         <v>86</v>
       </c>
-      <c r="C85" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" s="2">
+      <c r="B87" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B86" s="2" t="s">
+      <c r="C87" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="1">
         <v>87</v>
       </c>
-      <c r="C86" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" s="2">
+      <c r="B88" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B87" s="2" t="s">
+      <c r="C88" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="1">
         <v>88</v>
       </c>
-      <c r="C87" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" s="2">
+      <c r="B89" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B88" s="2" t="s">
+      <c r="C89" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" s="1">
         <v>89</v>
       </c>
-      <c r="C88" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" s="2">
+      <c r="B90" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B89" s="2" t="s">
+      <c r="C90" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="1">
         <v>90</v>
       </c>
-      <c r="C89" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" s="2">
+      <c r="B91" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B90" s="2" t="s">
+      <c r="C91" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="1">
         <v>91</v>
       </c>
-      <c r="C90" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" s="2">
+      <c r="B92" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B91" s="2" t="s">
+      <c r="C92" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="1">
         <v>92</v>
       </c>
-      <c r="C91" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" s="2">
+      <c r="B93" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B92" s="2" t="s">
+      <c r="C93" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="1">
         <v>93</v>
       </c>
-      <c r="C92" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" s="2">
+      <c r="B94" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B93" s="2" t="s">
+      <c r="C94" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="1">
         <v>94</v>
       </c>
-      <c r="C93" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" s="2">
+      <c r="B95" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B94" s="2" t="s">
+      <c r="C95" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" s="1">
         <v>95</v>
       </c>
-      <c r="C94" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95" s="2">
+      <c r="B96" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B95" s="2" t="s">
+      <c r="C96" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="1">
         <v>96</v>
       </c>
-      <c r="C95" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96" s="2">
+      <c r="B97" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B96" s="2" t="s">
+      <c r="C97" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="1">
         <v>97</v>
       </c>
-      <c r="C96" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A97" s="2">
+      <c r="B98" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B97" s="2" t="s">
+      <c r="C98" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="1">
         <v>98</v>
       </c>
-      <c r="C97" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A98" s="2">
+      <c r="B99" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B98" s="2" t="s">
+      <c r="C99" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="1">
         <v>99</v>
       </c>
-      <c r="C98" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A99" s="2">
+      <c r="B100" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B99" s="2" t="s">
+      <c r="C100" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="1">
         <v>100</v>
       </c>
-      <c r="C99" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A100" s="2">
+      <c r="B101" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B100" s="2" t="s">
+      <c r="C101" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="1">
         <v>101</v>
       </c>
-      <c r="C100" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A101" s="2">
+      <c r="B102" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B101" s="2" t="s">
+      <c r="C102" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="1">
         <v>102</v>
       </c>
-      <c r="C101" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A102" s="2">
+      <c r="B103" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B102" s="2" t="s">
+      <c r="C103" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" s="1">
         <v>103</v>
       </c>
-      <c r="C102" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A103" s="2">
+      <c r="B104" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B103" s="2" t="s">
+      <c r="C104" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" s="1">
         <v>104</v>
       </c>
-      <c r="C103" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A104" s="2">
+      <c r="B105" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B104" s="2" t="s">
+      <c r="C105" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" s="1">
         <v>105</v>
       </c>
-      <c r="C104" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A105" s="2">
+      <c r="B106" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B105" s="2" t="s">
+      <c r="C106" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" s="1">
         <v>106</v>
       </c>
-      <c r="C105" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A106" s="2">
+      <c r="B107" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B106" s="2" t="s">
+      <c r="C107" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" s="1">
         <v>107</v>
       </c>
-      <c r="C106" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A107" s="2">
+      <c r="B108" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B107" s="2" t="s">
+      <c r="C108" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" s="1">
         <v>108</v>
       </c>
-      <c r="C107" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A108" s="2">
+      <c r="B109" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B108" s="2" t="s">
+      <c r="C109" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" s="1">
         <v>109</v>
       </c>
-      <c r="C108" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A109" s="2">
+      <c r="B110" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B109" s="2" t="s">
+      <c r="C110" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" s="1">
         <v>110</v>
       </c>
-      <c r="C109" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A110" s="2">
+      <c r="B111" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B110" s="2" t="s">
+      <c r="C111" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" s="1">
         <v>111</v>
       </c>
-      <c r="C110" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A111" s="2">
+      <c r="B112" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B111" s="2" t="s">
+      <c r="C112" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" s="1">
         <v>112</v>
       </c>
-      <c r="C111" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A112" s="2">
+      <c r="B113" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B112" s="2" t="s">
+      <c r="C113" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" s="1">
         <v>113</v>
       </c>
-      <c r="C112" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A113" s="2">
+      <c r="B114" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B113" s="2" t="s">
+      <c r="C114" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" s="1">
         <v>114</v>
       </c>
-      <c r="C113" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A114" s="2">
+      <c r="B115" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B114" s="2" t="s">
+      <c r="C115" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" s="1">
         <v>115</v>
       </c>
-      <c r="C114" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A115" s="2">
+      <c r="B116" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B115" s="2" t="s">
+      <c r="C116" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" s="1">
         <v>116</v>
       </c>
-      <c r="C115" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A116" s="2">
+      <c r="B117" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B116" s="2" t="s">
+      <c r="C117" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" s="1">
         <v>117</v>
       </c>
-      <c r="C116" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A117" s="2">
+      <c r="B118" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B117" s="2" t="s">
+      <c r="C118" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" s="1">
         <v>118</v>
       </c>
-      <c r="C117" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A118" s="2">
+      <c r="B119" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B118" s="2" t="s">
+      <c r="C119" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" s="1">
         <v>119</v>
       </c>
-      <c r="C118" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A119" s="2">
+      <c r="B120" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B119" s="2" t="s">
+      <c r="C120" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" s="1">
         <v>120</v>
       </c>
-      <c r="C119" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A120" s="2">
+      <c r="B121" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B120" s="2" t="s">
+      <c r="C121" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" s="1">
         <v>121</v>
       </c>
-      <c r="C120" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A121" s="2">
+      <c r="B122" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B121" s="2" t="s">
+      <c r="C122" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" s="1">
         <v>122</v>
       </c>
-      <c r="C121" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A122" s="2">
+      <c r="B123" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B122" s="2" t="s">
+      <c r="C123" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" s="1">
         <v>123</v>
       </c>
-      <c r="C122" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A123" s="2">
+      <c r="B124" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B123" s="2" t="s">
+      <c r="C124" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" s="1">
         <v>124</v>
       </c>
-      <c r="C123" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A124" s="2">
+      <c r="B125" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B124" s="2" t="s">
+      <c r="C125" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" s="1">
         <v>125</v>
       </c>
-      <c r="C124" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A125" s="2">
+      <c r="B126" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B125" s="2" t="s">
+      <c r="C126" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" s="1">
         <v>126</v>
       </c>
-      <c r="C125" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A126" s="2">
+      <c r="B127" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B126" s="2" t="s">
+      <c r="C127" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" s="1">
         <v>127</v>
       </c>
-      <c r="C126" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A127" s="2">
+      <c r="B128" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B127" s="2" t="s">
+      <c r="C128" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" s="1">
         <v>128</v>
       </c>
-      <c r="C127" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A128" s="2">
+      <c r="B129" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B128" s="2" t="s">
+      <c r="C129" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" s="1">
         <v>129</v>
       </c>
-      <c r="C128" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A129" s="2">
+      <c r="B130" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B129" s="2" t="s">
+      <c r="C130" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" s="1">
         <v>130</v>
       </c>
-      <c r="C129" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A130" s="2">
+      <c r="B131" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B130" s="2" t="s">
+      <c r="C131" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" s="1">
         <v>131</v>
       </c>
-      <c r="C130" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A131" s="2">
+      <c r="B132" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B131" s="2" t="s">
+      <c r="C132" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" s="1">
         <v>132</v>
       </c>
-      <c r="C131" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A132" s="2">
+      <c r="B133" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B132" s="2" t="s">
+      <c r="C133" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" s="1">
         <v>133</v>
       </c>
-      <c r="C132" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A133" s="2">
+      <c r="B134" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B133" s="2" t="s">
+      <c r="C134" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" s="1">
         <v>134</v>
       </c>
-      <c r="C133" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A134" s="2">
+      <c r="B135" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B134" s="2" t="s">
+      <c r="C135" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" s="1">
         <v>135</v>
       </c>
-      <c r="C134" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A135" s="2">
+      <c r="B136" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B135" s="2" t="s">
+      <c r="C136" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" s="1">
         <v>136</v>
       </c>
-      <c r="C135" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A136" s="2">
+      <c r="B137" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B136" s="2" t="s">
+      <c r="C137" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" s="1">
         <v>137</v>
       </c>
-      <c r="C136" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A137" s="2">
+      <c r="B138" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B137" s="2" t="s">
+      <c r="C138" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" s="1">
         <v>138</v>
       </c>
-      <c r="C137" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A138" s="2">
+      <c r="B139" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="B138" s="2" t="s">
+      <c r="C139" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" s="1">
         <v>139</v>
       </c>
-      <c r="C138" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A139" s="2">
+      <c r="B140" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B139" s="2" t="s">
+      <c r="C140" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" s="1">
         <v>140</v>
       </c>
-      <c r="C139" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A140" s="2">
+      <c r="B141" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B140" s="2" t="s">
+      <c r="C141" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" s="1">
         <v>141</v>
       </c>
-      <c r="C140" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A141" s="2">
+      <c r="B142" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B141" s="2" t="s">
+      <c r="C142" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" s="1">
         <v>142</v>
       </c>
-      <c r="C141" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A142" s="2">
+      <c r="B143" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B142" s="2" t="s">
+      <c r="C143" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" s="1">
         <v>143</v>
       </c>
-      <c r="C142" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A143" s="2">
+      <c r="B144" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B143" s="2" t="s">
+      <c r="C144" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" s="1">
         <v>144</v>
       </c>
-      <c r="C143" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A144" s="2">
+      <c r="B145" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B144" s="2" t="s">
+      <c r="C145" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" s="1">
         <v>145</v>
       </c>
-      <c r="C144" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A145" s="2">
+      <c r="B146" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B145" s="2" t="s">
+      <c r="C146" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147" s="1">
         <v>146</v>
       </c>
-      <c r="C145" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A146" s="2">
+      <c r="B147" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="B146" s="2" t="s">
+      <c r="C147" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" s="1">
         <v>147</v>
       </c>
-      <c r="C146" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A147" s="2">
+      <c r="B148" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B147" s="2" t="s">
+      <c r="C148" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" s="1">
         <v>148</v>
       </c>
-      <c r="C147" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A148" s="2">
+      <c r="B149" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B148" s="2" t="s">
+      <c r="C149" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150" s="1">
         <v>149</v>
       </c>
-      <c r="C148" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A149" s="2">
+      <c r="B150" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B149" s="2" t="s">
+      <c r="C150" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" s="1">
         <v>150</v>
       </c>
-      <c r="C149" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A150" s="2">
+      <c r="B151" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B150" s="2" t="s">
+      <c r="C151" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" s="1">
         <v>151</v>
       </c>
-      <c r="C150" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A151" s="2">
+      <c r="B152" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B151" s="2" t="s">
+      <c r="C152" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" s="1">
         <v>152</v>
       </c>
-      <c r="C151" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A152" s="2">
+      <c r="B153" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="B152" s="2" t="s">
+      <c r="C153" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" s="1">
         <v>153</v>
       </c>
-      <c r="C152" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A153" s="2">
+      <c r="B154" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B153" s="2" t="s">
+      <c r="C154" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" s="1">
         <v>154</v>
       </c>
-      <c r="C153" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A154" s="2">
+      <c r="B155" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="B154" s="2" t="s">
+      <c r="C155" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156" s="1">
         <v>155</v>
       </c>
-      <c r="C154" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A155" s="2">
+      <c r="B156" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B155" s="2" t="s">
+      <c r="C156" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157" s="1">
         <v>156</v>
       </c>
-      <c r="C155" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A156" s="2">
+      <c r="B157" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B156" s="2" t="s">
+      <c r="C157" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" s="1">
         <v>157</v>
       </c>
-      <c r="C156" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A157" s="2">
+      <c r="B158" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B157" s="2" t="s">
+      <c r="C158" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159" s="1">
         <v>158</v>
       </c>
-      <c r="C157" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A158" s="2">
+      <c r="B159" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="B158" s="2" t="s">
+      <c r="C159" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160" s="1">
         <v>159</v>
       </c>
-      <c r="C158" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A159" s="2">
+      <c r="B160" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B159" s="2" t="s">
+      <c r="C160" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161" s="1">
         <v>160</v>
       </c>
-      <c r="C159" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A160" s="2">
+      <c r="B161" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="B160" s="2" t="s">
+      <c r="C161" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162" s="1">
         <v>161</v>
       </c>
-      <c r="C160" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A161" s="2">
+      <c r="B162" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B161" s="2" t="s">
+      <c r="C162" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" s="1">
         <v>162</v>
       </c>
-      <c r="C161" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A162" s="2">
+      <c r="B163" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="B162" s="2" t="s">
+      <c r="C163" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164" s="1">
         <v>163</v>
       </c>
-      <c r="C162" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A163" s="2">
+      <c r="B164" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B163" s="2" t="s">
+      <c r="C164" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165" s="1">
         <v>164</v>
       </c>
-      <c r="C163" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A164" s="2">
+      <c r="B165" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="B164" s="2" t="s">
+      <c r="C165" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166" s="1">
         <v>165</v>
       </c>
-      <c r="C164" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A165" s="2">
+      <c r="B166" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B165" s="2" t="s">
+      <c r="C166" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167" s="1">
         <v>166</v>
       </c>
-      <c r="C165" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A166" s="2">
+      <c r="B167" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B166" s="2" t="s">
+      <c r="C167" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168" s="1">
         <v>167</v>
       </c>
-      <c r="C166" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A167" s="2">
+      <c r="B168" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B167" s="2" t="s">
+      <c r="C168" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169" s="1">
         <v>168</v>
       </c>
-      <c r="C167" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A168" s="2">
+      <c r="B169" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="B168" s="2" t="s">
+      <c r="C169" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170" s="1">
         <v>169</v>
       </c>
-      <c r="C168" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A169" s="2">
+      <c r="B170" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B169" s="2" t="s">
+      <c r="C170" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A171" s="1">
         <v>170</v>
       </c>
-      <c r="C169" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A170" s="2">
+      <c r="B171" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="B170" s="2" t="s">
+      <c r="C171" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172" s="1">
         <v>171</v>
       </c>
-      <c r="C170" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A171" s="2">
+      <c r="B172" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="B171" s="2" t="s">
+      <c r="C172" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173" s="1">
         <v>172</v>
       </c>
-      <c r="C171" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A172" s="2">
+      <c r="B173" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B172" s="2" t="s">
+      <c r="C173" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A174" s="1">
         <v>173</v>
       </c>
-      <c r="C172" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A173" s="2">
+      <c r="B174" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B173" s="2" t="s">
+      <c r="C174" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175" s="1">
         <v>174</v>
       </c>
-      <c r="C173" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A174" s="2">
+      <c r="B175" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="B174" s="2" t="s">
+      <c r="C175" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176" s="1">
         <v>175</v>
       </c>
-      <c r="C174" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A175" s="2">
+      <c r="B176" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B175" s="2" t="s">
+      <c r="C176" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A177" s="1">
         <v>176</v>
       </c>
-      <c r="C175" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A176" s="2">
+      <c r="B177" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="B176" s="2" t="s">
+      <c r="C177" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178" s="1">
         <v>177</v>
       </c>
-      <c r="C176" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A177" s="2">
+      <c r="B178" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B177" s="2" t="s">
+      <c r="C178" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179" s="1">
         <v>178</v>
       </c>
-      <c r="C177" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A178" s="2">
+      <c r="B179" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="B178" s="2" t="s">
+      <c r="C179" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180" s="1">
         <v>179</v>
       </c>
-      <c r="C178" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A179" s="2">
+      <c r="B180" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="B179" s="2" t="s">
+      <c r="C180" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181" s="1">
         <v>180</v>
       </c>
-      <c r="C179" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A180" s="2">
+      <c r="B181" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="B180" s="2" t="s">
+      <c r="C181" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182" s="1">
         <v>181</v>
       </c>
-      <c r="C180" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A181" s="2">
+      <c r="B182" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="B181" s="2" t="s">
+      <c r="C182" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A183" s="1">
         <v>182</v>
       </c>
-      <c r="C181" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A182" s="2">
+      <c r="B183" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="B182" s="2" t="s">
+      <c r="C183" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184" s="1">
         <v>183</v>
       </c>
-      <c r="C182" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A183" s="2">
+      <c r="B184" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="B183" s="2" t="s">
+      <c r="C184" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A185" s="1">
         <v>184</v>
       </c>
-      <c r="C183" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A184" s="2">
+      <c r="B185" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="B184" s="2" t="s">
+      <c r="C185" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A186" s="1">
         <v>185</v>
       </c>
-      <c r="C184" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A185" s="2">
+      <c r="B186" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="B185" s="2" t="s">
+      <c r="C186" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A187" s="1">
         <v>186</v>
       </c>
-      <c r="C185" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A186" s="2">
+      <c r="B187" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B186" s="2" t="s">
+      <c r="C187" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A188" s="1">
         <v>187</v>
       </c>
-      <c r="C186" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A187" s="2">
+      <c r="B188" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="B187" s="2" t="s">
+      <c r="C188" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A189" s="1">
         <v>188</v>
       </c>
-      <c r="C187" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A188" s="2">
+      <c r="B189" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="B188" s="2" t="s">
+      <c r="C189" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A190" s="1">
         <v>189</v>
       </c>
-      <c r="C188" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A189" s="2">
+      <c r="B190" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="B189" s="2" t="s">
+      <c r="C190" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A191" s="1">
         <v>190</v>
       </c>
-      <c r="C189" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A190" s="2">
+      <c r="B191" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="B190" s="2" t="s">
+      <c r="C191" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A192" s="1">
         <v>191</v>
       </c>
-      <c r="C190" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A191" s="2">
+      <c r="B192" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="B191" s="2" t="s">
+      <c r="C192" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193" s="1">
         <v>192</v>
       </c>
-      <c r="C191" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A192" s="2">
+      <c r="B193" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="B192" s="2" t="s">
+      <c r="C193" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194" s="1">
         <v>193</v>
       </c>
-      <c r="C192" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A193" s="2">
+      <c r="B194" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="B193" s="2" t="s">
+      <c r="C194" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A195" s="1">
         <v>194</v>
       </c>
-      <c r="C193" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A194" s="2">
+      <c r="B195" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="B194" s="2" t="s">
+      <c r="C195" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196" s="1">
         <v>195</v>
       </c>
-      <c r="C194" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A195" s="2">
+      <c r="B196" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="B195" s="2" t="s">
+      <c r="C196" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197" s="1">
         <v>196</v>
       </c>
-      <c r="C195" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A196" s="2">
+      <c r="B197" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="B196" s="2" t="s">
+      <c r="C197" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A198" s="1">
         <v>197</v>
       </c>
-      <c r="C196" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A197" s="2">
+      <c r="B198" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="B197" s="2" t="s">
+      <c r="C198" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A199" s="1">
         <v>198</v>
       </c>
-      <c r="C197" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A198" s="2">
+      <c r="B199" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B198" s="2" t="s">
+      <c r="C199" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A200" s="1">
         <v>199</v>
       </c>
-      <c r="C198" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A199" s="2">
+      <c r="B200" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B199" s="2" t="s">
+      <c r="C200" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A201" s="1">
         <v>200</v>
       </c>
-      <c r="C199" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A200" s="2">
+      <c r="B201" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B200" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="C200" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A201" s="2">
-        <v>200</v>
-      </c>
-      <c r="B201" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="C201" s="2" t="s">
-        <v>203</v>
+      <c r="C201" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Cardiologie/Excel/cardio_14.xlsx
+++ b/Cardiologie/Excel/cardio_14.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moito\Desktop\Sérieux\Projet\Site web\Cardiologie\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7F56317-9B7E-48DA-A1E6-2A49215CAF8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE878B5D-534E-401B-91D1-86A56EA75030}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="405">
   <si>
     <t>Le réseau veineux des membres inférieurs comprend un réseau superficiel et un réseau profond.</t>
   </si>
@@ -641,6 +641,600 @@
   </si>
   <si>
     <t>image</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le réseau veineux comprend un réseau superficiel et un réseau profond </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les réseaux superficiel et profond sont reliés par des veines communicantes ou perforantes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le réseau superficiel draine au contraire 1/10 du sang veineux </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le sang est normalement drainé de la superficie vers la profondeur </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les saphènes appartiennent au réseau superficiel (le profond est dit aponévrotique) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Des valvules parsèment les veines superficielles, profondes et communicantes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les valvules servent à éviter un reflux (elles dirigent normalement le sang de la superficie vers la profondeur) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La varice est au contraire une dilatation permanente pathologique d’une veine superficielle </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'insuffisance veineuse est un syndrome associé à diverses anomalies (varices, reflux, obstacles, etc.) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le réseau superficiel draine effectivement 1/10 du sang veineux des membres inférieurs </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est un syndrome associant des signes en rapport avec une anomalie anatomique ou fonctionnelle permanente </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle peut être liée à diverses causes dont les malformations congénitales </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La prévalence augmente au contraire avec l'âge (affecte 35% des actifs et plus de la moitié des retraités) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L’insuffisance veineuse affecte effectivement 35% des Européens actifs </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle affecte effectivement plus de la moitié des retraités </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte cite les saphènes pour le superficiel ; fémorale et poplitée ne sont pas spécifiées dans ce rappel </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il existe au contraire une nette prédominance féminine (3 femmes pour 1 homme) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'insuffisance veineuse chronique peut être liée à un reflux, un obstacle ou une compression </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document confirme que dans les pays industrialisés, 1 femme sur 2 est ou sera atteinte </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Environ 1% (et non 10%) de la population souffrira un jour d’une ulcération d’origine veineuse </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toute dysfonction de la pompe musculaire surale peut causer une insuffisance veineuse </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La prédominance féminine est de 3 femmes pour 1 homme </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La prévalence des varices dans la population adulte varie entre 9 et 30% </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ces pathologies représentent effectivement près de 2% du budget des soins de santé </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le traitement des ulcères chroniques aux USA représente 1 milliard (et non 50 millions) de dollars par an </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La prévalence des varices peut effectivement atteindre 30% </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La différence de pression diminue à la marche (de 80 mmHg à 15-30 mmHg) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le fait d'être bipède facilite le développement d'une insuffisance veineuse </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La pression hydrostatique en position immobile est effectivement d’environ 80 mmHg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les valvules préviennent au contraire tout déplacement centrifuge (reflux) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le sang de la semelle veineuse est comprimé à chaque pas et déplacé vers le mollet </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La pompe respiratoire facilite le retour veineux vers la cage thoracique (sans précision de la phase) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte dit que l'espèce humaine la développe "facilement" car elle est bipède </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La pression hydrostatique au niveau du pied à la marche est effectivement de 15 à 30 mmHg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le flux dépend de la contraction des muscles au sein d’aponévroses inextensibles </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'insuffisance veineuse primaire a effectivement une composante héréditaire probable </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La stase et le flux rétrograde ont au contraire un effet proinflammatoire et prothrombotique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le flux laminaire normal est antioxydant ; le flux turbulent est proinflammatoire </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le contenu en collagène augmente au contraire, rendant la veine plus rigide </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La dégradation de la matrice extracellulaire est causée par les cellules inflammatoires </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le syndrome post-thrombotique est une cause majeure d'insuffisance veineuse secondaire </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'agénésie ou hypoplasie valvulaire est citée comme une cause de dysplasie veineuse </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les tumeurs peuvent effectivement comprimer les veines et causer une insuffisance secondaire </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le syndrome de Cockett est cité comme une cause de compression, mais noté comme "rarement" </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le syndrome de Cockett n'est pas détaillé, le texte cite juste une compression par tumeur ou Cockett </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle induit une insuffisance secondaire via des facteurs hormonaux ET hémodynamiques </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les sportifs sont cités comme une cause hémodynamique d'insuffisance veineuse secondaire </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La pression hydrostatique au niveau du pied descend effectivement à 15-30 mmHg à la marche </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle dépend de la contraction des muscles jambiers lors de la marche </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'insuffisance veineuse primaire a une composante héréditaire probable </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La stase et le flux rétrograde ont un effet proinflammatoire et prothrombotique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'augmentation du collagène et la désorganisation des fibres élastiques rigidifient la veine </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'insuffisance veineuse primaire est par définition non séquellaire </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le flux veineux turbulent a effectivement un effet proinflammatoire sur la paroi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les altérations constitutionnelles ne sont au contraire pas séquellaires </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elles sont citées comme une cause d'insuffisance veineuse secondaire </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'hérédité est une composante probable mais d'autres facteurs de risque existent </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La réduction du flux a un effet proinflammatoire sur les cellules endothéliales </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'amincissement de la paroi et la dégradation de la matrice permettent l'extravasation </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'insuffisance primaire ne fait par définition pas suite à une thrombose </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La pression hydrostatique diminue à la marche mais ne disparaît pas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ces éléments génèrent au contraire un flux sanguin centripède </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La pompe respiratoire facilite effectivement le retour veineux vers le thorax </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les valvules et pompes dirigent le flux vers le haut et empêchent le reflux </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle est explicitement listée comme une cause de dysfonction veineuse </t>
+  </si>
+  <si>
+    <t xml:space="preserve">On propose au maximum une contention de classe II pour ces cas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le flux laminaire normal a au contraire une action anti-inflammatoire </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'hypertrophie s'accompagne d'une hausse du collagène et d'une désorganisation cellulaire </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les dépôts d'hémosidérine sont au contraire pro-inflammatoires </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La paroi est hypertrophiée à certains endroits et amincie (atrophie) à d'autres </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les cellules inflammatoires dégradent la matrice extracellulaire (et non les myocytes) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La pression hydrostatique au pied descend au contraire vers 15 à 30 mmHg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il est cité comme une cause de compression veineuse secondaire </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ces deux éléments sont listés parmi les principaux facteurs de risque </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte confirme que ces antécédents augmentent le risque d'insuffisance </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'orthostatisme prolongé est au contraire un facteur de risque environnemental </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le sexe féminin et la grossesse sont des facteurs de risque identifiés </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'exposition solaire provoque une vasodilatation qui aggrave la maladie </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les manifestations sont au contraire très variables d'un patient à l'autre </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les douleurs jambières sont au contraire diminuées par la surélévation </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'oedème péri-malléolaire a au contraire tendance à s'accentuer en cours de journée </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le système CEAP évalue effectivement ces quatre paramètres </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La classification clinique C s'étend au contraire de 0 à 6 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les varices réticulaires sont de petit calibre et non palpables </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'oedème correspond au stade 3 de la classification clinique CEAP </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est une complication trophique résultant de la stase veineuse chronique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'atrophie blanche correspond à une zone d'ischémie cutanée localisée </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les télangiectasies sont au contraire des dilatations intradermiques </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les ulcères veineux sont au contraire le plus souvent peu douloureux </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leur siège préférentiel est au contraire la région péri-malléolaire interne </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le spectre clinique s'étend de la simple pesanteur jusqu'à l'ulcère </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les perles variqueuses sont des dilatations veineuses superficielles </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La sensibilité le long des veines dilatées est un signe clinique possible </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ces symptômes font partie des premières manifestations cliniques citées </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle peut effectivement provoquer des crampes nocturnes et du prurit </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le stade 0 désigne les sujets sans signe clinique visible ou palpable </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document ne mentionne pas la durée médiane de cicatrisation </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce sont effectivement des dilatations intradermiques des plexus sous-papillaires </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les télangiectasies de 0,4 à 1 mm sont au contraire généralement de couleur bleue </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est le stade C2 qui désigne les varices de plus de 3 mm, lesquelles sont palpables </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document précise au contraire que ces télangiectasies ont une couleur rouge </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ces caractéristiques (réticulaires, petit calibre, non palpables) définissent le stade C1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le stade C3 de la classification CEAP correspond effectivement à la présence d’oedème </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle est décrite comme une dermatose prurigineuse (qui gratte) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle est au contraire la conséquence d'une hyperpression veineuse (stase) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'hypodermite est effectivement une fibrose progressive suite à des épisodes répétés </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'atrophie blanche est causée par l'occlusion d'artérioles du derme superficiel </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il se présente comme une dermatose érythémato-vésiculeuse, suintante, en nappes ou placards </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les varices peuvent effectivement se compliquer d'une thrombose superficielle </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle est causée par une occlusion d'artérioles et non par une occlusion veineuse </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le stade C2 correspond effectivement à des varices de plus de 3 mm, palpables </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le stade C6 correspond au contraire à un ulcère veineux actif (C5 est cicatrisé) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le stade C4 correspond effectivement aux troubles trophiques cutanés </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le stade C1 inclut effectivement les télangiectasies et les varices réticulaires </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'échelle de gravité (C0 à C6) prend effectivement en compte ces facteurs </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il fait au contraire partie des premières manifestations cliniques citées </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ces dilatations veineuses sont effectivement citées comme les premières manifestations </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La dermite ocre est bien une complication trophique de la stase </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle correspond à une pigmentation brunâtre (pas bleutée) due à l'hémosidérine </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle résulte de l'hyperpression veineuse et de l'extravasation de globules rouges </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le terme "guêtre de cheval" n'apparaît pas dans le texte fourni </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La fibrose progressive concerne le tissu sous-cutané (lipodermatosclérose) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'eczéma variqueux se situe effectivement en regard d'une varice </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est une dermatose prurigineuse (et non non prurigineuse) érythémato-vésiculeuse </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le siège préférentiel des ulcères est la région péri-malléolaire interne </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les ulcères veineux sont au contraire décrits comme peu douloureux </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte confirme que les ulcères ont des bords fibreux et sont suintants ou rouges </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elles se compliquent exceptionnellement (et non très souvent) d'une TVP </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les varices peuvent effectivement se rompre et saigner suite à un traumatisme </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte indique au contraire que la maladie améliore difficilement sa qualité de vie </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le stade C5 correspond au contraire à un ulcère cicatrisé </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document ne fournit pas de statistique sur la durée médiane de cicatrisation </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document ne contient pas cette statistique temporelle </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte mentionne que les ulcères récidivent effectivement très fréquemment </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'anamnèse doit effectivement rechercher ces facteurs et antécédents </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'examen doit au contraire être réalisé en position debout </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il teste la continence des valvules sur les axes saphéniens (superficiels) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les varices sont souvent idiopathiques mais peuvent être secondaires (TVP, etc.) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document ne précise pas que l'oedème péri-malléolaire est un signe spécifique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La phlébographie n'est au contraire quasi plus jamais justifiée </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'échographie-Doppler apporte effectivement des éléments confortant le diagnostic </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elles ont un intérêt très limité et ne sont qu'un complément </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L’exercice physique permet effectivement de diminuer la pression veineuse de 2/3 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La contention élève au contraire la pression tissulaire </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La pression doit être plus forte à la cheville qu'en proximal (dégressive) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les stations debout prolongées sont au contraire listées dans les effets défavorables </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le traitement des varices est varié (scléroses, chirurgie, laser, radiofréquence) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document confirme que les ulcères sont soignés par des pansements adéquats </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'examen clinique pour détecter les varices doit être réalisé en position debout </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le test de Schwartz permet effectivement d'évaluer la continence des valvules saphéniennes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte précise que les varices sont effectivement souvent idiopathiques </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le diagnostic différentiel de l'oedème inclut le lymphoedème, les causes cardiaques ou rénales </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'examen doit être réalisé en position debout pour constater l'existence de varices </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document précise au contraire que cet examen ne permet pas de poser le diagnostic de façon formelle </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le décubitus et la surélévation sont les principes essentiels de lutte contre la stase </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La pression doit être dégressive : plus forte à la cheville qu'en proximal pour éviter l'effet garrot </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les douches d'eau froide matin et soir sont recommandées pour leur effet vasoconstricteur </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document précise au contraire que le traitement est mal codifié et dépend du spécialiste </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Des greffes cutanées sont effectivement citées comme option pour le soin des ulcères </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'exposition à des sources de chaleur (sauna, soleil) est à éviter car elle entraîne une vasodilatation </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'insuffisance veineuse peut être favorisée par la manœuvre de Valsalva (chronique chez les sportifs) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le signe du flot (ou test de Schwartz) étudie la transmission de l'onde de choc sur les axes saphéniens </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La percussion et la réception de l'onde se font effectivement avec les doigts des deux mains </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chez le sujet sain, la percussion ne doit transmettre l'onde que vers l'aval (vers le haut) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La transmission d'une onde vers l'amont (vers le bas) trahit une insuffisance valvulaire </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Normalement, l'onde ne doit jamais être perçue vers l'amont (le bas de la jambe) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Une onde transmise vers le bas (amont) est le signe d'une incontinence valvulaire </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Une onde transmise vers l'aval (le haut de la jambe) est le résultat normal chez le sujet sain </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il faut s'assurer que les ulcères sont d'origine veineuse et non liés à une AOMI avant de surélever les membres </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte cite l'oedème cyclique idiopathique de la femme jeune comme diagnostic différentiel </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document indique que l'examen est chronophage (prend du temps) pour peu de bénéfice </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'échographie Doppler est au contraire utile pour réaliser une cartographie veineuse précise </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'examen est réalisé systématiquement lorsqu'une résection chirurgicale est envisagée </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La phlébographie est un bilan complémentaire invasif </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cet examen invasif n'est au contraire quasi plus jamais justifié </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La surélévation et le décubitus constituent effectivement le traitement de base des ulcères </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ces activités physiques permettent effectivement de réduire l'hypertension veineuse </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les stations assises prolongées sont au contraire listées parmi les effets défavorables </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La surélévation recommandée pour les pieds du lit la nuit est de 10-15 cm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La lutte contre la surcharge pondérale est un conseil d'hygiène de vie recommandé </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La contention augmente la pression tissulaire, ce qui diminue au contraire le différentiel avec la pression capillaire </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cette normalisation de la chute de pression différentielle traite la micro-angiopathie </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La contention diminue au contraire le diamètre des varices et leur reflux </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document ne mentionne pas de pression spécifique pour les bas de soutien </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ces bas ont une action définie par le nombre de deniers et ne sont pas réglementés </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'action des bas de soutien est définie par le nombre de deniers, pas la classe I </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les bas de classe III appliquent une pression de 30-45 mmHg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les bas de classe II appliquent effectivement une pression de 20-30 mmHg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">En cas d'insuffisance veineuse ou de varices, on propose au maximum la classe II </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toute dysfonction de la pompe musculaire surale est citée comme une cause de l'insuffisance </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le port de talons hauts est au contraire déconseillé car il ralentit le retour veineux </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ces deux éléments sont listés comme ayant un effet défavorable sur le retour veineux </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les veinotropes ont effectivement un intérêt très limité et ne sont qu'un complément </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte énumère effectivement ces différents moyens thérapeutiques </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le stripping est une technique chirurgicale de traitement des varices </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte recommande des infirmières ou médecins rompus aux techniques de pansements </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les stations debout et assise prolongées doivent être évitées dans la mesure du possible </t>
+  </si>
+  <si>
+    <t>Page</t>
   </si>
 </sst>
 </file>
@@ -988,7 +1582,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G201"/>
+  <dimension ref="A1:H201"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
@@ -997,7 +1591,7 @@
     <col min="4" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>200</v>
       </c>
@@ -1011,16 +1605,19 @@
         <v>203</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1030,8 +1627,14 @@
       <c r="C2" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D2" t="s">
+        <v>207</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1041,8 +1644,14 @@
       <c r="C3" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D3" t="s">
+        <v>208</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1052,8 +1661,14 @@
       <c r="C4" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D4" t="s">
+        <v>209</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1063,8 +1678,14 @@
       <c r="C5" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D5" t="s">
+        <v>210</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1074,8 +1695,14 @@
       <c r="C6" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D6" t="s">
+        <v>211</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1085,8 +1712,14 @@
       <c r="C7" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D7" t="s">
+        <v>212</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1096,8 +1729,14 @@
       <c r="C8" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D8" t="s">
+        <v>213</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1107,8 +1746,14 @@
       <c r="C9" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D9" t="s">
+        <v>214</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1118,8 +1763,14 @@
       <c r="C10" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D10" t="s">
+        <v>215</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -1129,8 +1780,14 @@
       <c r="C11" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D11" t="s">
+        <v>216</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -1140,8 +1797,14 @@
       <c r="C12" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D12" t="s">
+        <v>217</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -1151,8 +1814,14 @@
       <c r="C13" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D13" t="s">
+        <v>218</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -1162,8 +1831,14 @@
       <c r="C14" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D14" t="s">
+        <v>219</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -1173,8 +1848,14 @@
       <c r="C15" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D15" t="s">
+        <v>220</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -1184,8 +1865,14 @@
       <c r="C16" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D16" t="s">
+        <v>221</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -1195,8 +1882,14 @@
       <c r="C17" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D17" t="s">
+        <v>222</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -1206,8 +1899,14 @@
       <c r="C18" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D18" t="s">
+        <v>223</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -1217,8 +1916,14 @@
       <c r="C19" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D19" t="s">
+        <v>224</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -1228,8 +1933,14 @@
       <c r="C20" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D20" t="s">
+        <v>225</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -1239,8 +1950,14 @@
       <c r="C21" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D21" t="s">
+        <v>226</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -1250,8 +1967,14 @@
       <c r="C22" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D22" t="s">
+        <v>227</v>
+      </c>
+      <c r="E22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -1261,8 +1984,14 @@
       <c r="C23" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D23" t="s">
+        <v>228</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -1272,8 +2001,14 @@
       <c r="C24" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D24" t="s">
+        <v>229</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -1283,8 +2018,14 @@
       <c r="C25" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D25" t="s">
+        <v>230</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -1294,8 +2035,14 @@
       <c r="C26" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D26" t="s">
+        <v>231</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -1305,8 +2052,14 @@
       <c r="C27" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D27" t="s">
+        <v>220</v>
+      </c>
+      <c r="E27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -1316,8 +2069,14 @@
       <c r="C28" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D28" t="s">
+        <v>232</v>
+      </c>
+      <c r="E28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -1327,8 +2086,14 @@
       <c r="C29" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D29" t="s">
+        <v>233</v>
+      </c>
+      <c r="E29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -1338,8 +2103,14 @@
       <c r="C30" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D30" t="s">
+        <v>234</v>
+      </c>
+      <c r="E30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -1349,8 +2120,14 @@
       <c r="C31" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D31" t="s">
+        <v>235</v>
+      </c>
+      <c r="E31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -1360,8 +2137,14 @@
       <c r="C32" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D32" t="s">
+        <v>236</v>
+      </c>
+      <c r="E32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -1371,8 +2154,14 @@
       <c r="C33" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D33" t="s">
+        <v>212</v>
+      </c>
+      <c r="E33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -1382,8 +2171,14 @@
       <c r="C34" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D34" t="s">
+        <v>237</v>
+      </c>
+      <c r="E34">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -1393,8 +2188,14 @@
       <c r="C35" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D35" t="s">
+        <v>238</v>
+      </c>
+      <c r="E35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -1404,8 +2205,14 @@
       <c r="C36" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D36" t="s">
+        <v>239</v>
+      </c>
+      <c r="E36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -1415,8 +2222,14 @@
       <c r="C37" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D37" t="s">
+        <v>240</v>
+      </c>
+      <c r="E37">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -1426,8 +2239,14 @@
       <c r="C38" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D38" t="s">
+        <v>241</v>
+      </c>
+      <c r="E38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -1437,8 +2256,14 @@
       <c r="C39" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D39" t="s">
+        <v>242</v>
+      </c>
+      <c r="E39">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -1448,8 +2273,14 @@
       <c r="C40" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D40" t="s">
+        <v>243</v>
+      </c>
+      <c r="E40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -1459,8 +2290,14 @@
       <c r="C41" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D41" t="s">
+        <v>244</v>
+      </c>
+      <c r="E41">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>41</v>
       </c>
@@ -1470,8 +2307,14 @@
       <c r="C42" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D42" t="s">
+        <v>245</v>
+      </c>
+      <c r="E42">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -1481,8 +2324,14 @@
       <c r="C43" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D43" t="s">
+        <v>246</v>
+      </c>
+      <c r="E43">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>43</v>
       </c>
@@ -1492,8 +2341,14 @@
       <c r="C44" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D44" t="s">
+        <v>247</v>
+      </c>
+      <c r="E44">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>44</v>
       </c>
@@ -1503,8 +2358,14 @@
       <c r="C45" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D45" t="s">
+        <v>248</v>
+      </c>
+      <c r="E45">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>45</v>
       </c>
@@ -1514,8 +2375,14 @@
       <c r="C46" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D46" t="s">
+        <v>249</v>
+      </c>
+      <c r="E46">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>46</v>
       </c>
@@ -1525,8 +2392,14 @@
       <c r="C47" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D47" t="s">
+        <v>250</v>
+      </c>
+      <c r="E47">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>47</v>
       </c>
@@ -1536,8 +2409,14 @@
       <c r="C48" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D48" t="s">
+        <v>251</v>
+      </c>
+      <c r="E48">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>48</v>
       </c>
@@ -1547,8 +2426,14 @@
       <c r="C49" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D49" t="s">
+        <v>252</v>
+      </c>
+      <c r="E49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>49</v>
       </c>
@@ -1558,8 +2443,14 @@
       <c r="C50" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D50" t="s">
+        <v>253</v>
+      </c>
+      <c r="E50">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>50</v>
       </c>
@@ -1569,8 +2460,14 @@
       <c r="C51" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D51" t="s">
+        <v>254</v>
+      </c>
+      <c r="E51">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>51</v>
       </c>
@@ -1580,8 +2477,14 @@
       <c r="C52" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D52" t="s">
+        <v>255</v>
+      </c>
+      <c r="E52" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>52</v>
       </c>
@@ -1591,8 +2494,14 @@
       <c r="C53" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D53" t="s">
+        <v>256</v>
+      </c>
+      <c r="E53" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>53</v>
       </c>
@@ -1602,8 +2511,14 @@
       <c r="C54" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D54" t="s">
+        <v>257</v>
+      </c>
+      <c r="E54" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>54</v>
       </c>
@@ -1613,8 +2528,14 @@
       <c r="C55" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D55" t="s">
+        <v>258</v>
+      </c>
+      <c r="E55" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>55</v>
       </c>
@@ -1624,8 +2545,14 @@
       <c r="C56" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D56" t="s">
+        <v>259</v>
+      </c>
+      <c r="E56" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>56</v>
       </c>
@@ -1635,8 +2562,14 @@
       <c r="C57" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D57" t="s">
+        <v>260</v>
+      </c>
+      <c r="E57" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>57</v>
       </c>
@@ -1646,8 +2579,14 @@
       <c r="C58" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D58" t="s">
+        <v>261</v>
+      </c>
+      <c r="E58" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>58</v>
       </c>
@@ -1657,8 +2596,14 @@
       <c r="C59" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D59" t="s">
+        <v>262</v>
+      </c>
+      <c r="E59" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>59</v>
       </c>
@@ -1668,8 +2613,14 @@
       <c r="C60" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D60" t="s">
+        <v>263</v>
+      </c>
+      <c r="E60" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>60</v>
       </c>
@@ -1679,8 +2630,14 @@
       <c r="C61" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D61" t="s">
+        <v>264</v>
+      </c>
+      <c r="E61" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>61</v>
       </c>
@@ -1690,8 +2647,14 @@
       <c r="C62" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D62" t="s">
+        <v>265</v>
+      </c>
+      <c r="E62" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>62</v>
       </c>
@@ -1701,8 +2664,14 @@
       <c r="C63" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D63" t="s">
+        <v>266</v>
+      </c>
+      <c r="E63" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>63</v>
       </c>
@@ -1712,8 +2681,14 @@
       <c r="C64" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D64" t="s">
+        <v>267</v>
+      </c>
+      <c r="E64" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>64</v>
       </c>
@@ -1723,8 +2698,14 @@
       <c r="C65" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D65" t="s">
+        <v>268</v>
+      </c>
+      <c r="E65" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>65</v>
       </c>
@@ -1734,8 +2715,14 @@
       <c r="C66" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D66" t="s">
+        <v>269</v>
+      </c>
+      <c r="E66" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>66</v>
       </c>
@@ -1745,8 +2732,14 @@
       <c r="C67" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D67" t="s">
+        <v>270</v>
+      </c>
+      <c r="E67" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>67</v>
       </c>
@@ -1756,8 +2749,14 @@
       <c r="C68" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D68" t="s">
+        <v>271</v>
+      </c>
+      <c r="E68" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>68</v>
       </c>
@@ -1767,8 +2766,14 @@
       <c r="C69" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D69" t="s">
+        <v>272</v>
+      </c>
+      <c r="E69" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>69</v>
       </c>
@@ -1778,8 +2783,14 @@
       <c r="C70" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D70" t="s">
+        <v>273</v>
+      </c>
+      <c r="E70" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>70</v>
       </c>
@@ -1789,8 +2800,14 @@
       <c r="C71" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D71" t="s">
+        <v>274</v>
+      </c>
+      <c r="E71" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>71</v>
       </c>
@@ -1800,8 +2817,14 @@
       <c r="C72" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D72" t="s">
+        <v>275</v>
+      </c>
+      <c r="E72" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>72</v>
       </c>
@@ -1811,8 +2834,14 @@
       <c r="C73" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D73" t="s">
+        <v>276</v>
+      </c>
+      <c r="E73" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>73</v>
       </c>
@@ -1822,8 +2851,14 @@
       <c r="C74" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D74" t="s">
+        <v>277</v>
+      </c>
+      <c r="E74" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>74</v>
       </c>
@@ -1833,8 +2868,14 @@
       <c r="C75" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D75" t="s">
+        <v>278</v>
+      </c>
+      <c r="E75" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>75</v>
       </c>
@@ -1844,8 +2885,14 @@
       <c r="C76" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D76" t="s">
+        <v>279</v>
+      </c>
+      <c r="E76" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>76</v>
       </c>
@@ -1855,8 +2902,14 @@
       <c r="C77" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D77" t="s">
+        <v>280</v>
+      </c>
+      <c r="E77" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>77</v>
       </c>
@@ -1866,8 +2919,14 @@
       <c r="C78" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D78" t="s">
+        <v>281</v>
+      </c>
+      <c r="E78" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>78</v>
       </c>
@@ -1877,8 +2936,14 @@
       <c r="C79" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D79" t="s">
+        <v>282</v>
+      </c>
+      <c r="E79" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>79</v>
       </c>
@@ -1888,8 +2953,14 @@
       <c r="C80" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D80" t="s">
+        <v>283</v>
+      </c>
+      <c r="E80" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>80</v>
       </c>
@@ -1899,8 +2970,14 @@
       <c r="C81" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D81" t="s">
+        <v>284</v>
+      </c>
+      <c r="E81" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>81</v>
       </c>
@@ -1910,8 +2987,14 @@
       <c r="C82" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D82" t="s">
+        <v>285</v>
+      </c>
+      <c r="E82" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>82</v>
       </c>
@@ -1921,8 +3004,14 @@
       <c r="C83" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D83" t="s">
+        <v>286</v>
+      </c>
+      <c r="E83" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>83</v>
       </c>
@@ -1932,8 +3021,14 @@
       <c r="C84" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D84" t="s">
+        <v>287</v>
+      </c>
+      <c r="E84" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>84</v>
       </c>
@@ -1943,8 +3038,14 @@
       <c r="C85" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D85" t="s">
+        <v>288</v>
+      </c>
+      <c r="E85" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>85</v>
       </c>
@@ -1954,8 +3055,14 @@
       <c r="C86" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D86" t="s">
+        <v>289</v>
+      </c>
+      <c r="E86" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>86</v>
       </c>
@@ -1965,8 +3072,14 @@
       <c r="C87" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D87" t="s">
+        <v>290</v>
+      </c>
+      <c r="E87" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>87</v>
       </c>
@@ -1976,8 +3089,14 @@
       <c r="C88" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D88" t="s">
+        <v>291</v>
+      </c>
+      <c r="E88" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>88</v>
       </c>
@@ -1987,8 +3106,14 @@
       <c r="C89" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D89" t="s">
+        <v>292</v>
+      </c>
+      <c r="E89" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>89</v>
       </c>
@@ -1998,8 +3123,14 @@
       <c r="C90" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D90" t="s">
+        <v>293</v>
+      </c>
+      <c r="E90" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>90</v>
       </c>
@@ -2009,8 +3140,14 @@
       <c r="C91" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D91" t="s">
+        <v>294</v>
+      </c>
+      <c r="E91" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>91</v>
       </c>
@@ -2020,8 +3157,14 @@
       <c r="C92" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D92" t="s">
+        <v>295</v>
+      </c>
+      <c r="E92" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>92</v>
       </c>
@@ -2031,8 +3174,14 @@
       <c r="C93" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D93" t="s">
+        <v>296</v>
+      </c>
+      <c r="E93" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>93</v>
       </c>
@@ -2042,8 +3191,14 @@
       <c r="C94" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D94" t="s">
+        <v>297</v>
+      </c>
+      <c r="E94" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>94</v>
       </c>
@@ -2053,8 +3208,14 @@
       <c r="C95" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D95" t="s">
+        <v>298</v>
+      </c>
+      <c r="E95" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>95</v>
       </c>
@@ -2064,8 +3225,14 @@
       <c r="C96" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D96" t="s">
+        <v>299</v>
+      </c>
+      <c r="E96" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>96</v>
       </c>
@@ -2075,8 +3242,14 @@
       <c r="C97" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D97" t="s">
+        <v>300</v>
+      </c>
+      <c r="E97" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>97</v>
       </c>
@@ -2086,8 +3259,14 @@
       <c r="C98" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D98" t="s">
+        <v>301</v>
+      </c>
+      <c r="E98" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>98</v>
       </c>
@@ -2097,8 +3276,14 @@
       <c r="C99" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D99" t="s">
+        <v>302</v>
+      </c>
+      <c r="E99" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>99</v>
       </c>
@@ -2108,8 +3293,14 @@
       <c r="C100" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D100" t="s">
+        <v>303</v>
+      </c>
+      <c r="E100" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>100</v>
       </c>
@@ -2119,8 +3310,14 @@
       <c r="C101" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D101" t="s">
+        <v>304</v>
+      </c>
+      <c r="E101" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>101</v>
       </c>
@@ -2130,8 +3327,14 @@
       <c r="C102" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D102" t="s">
+        <v>305</v>
+      </c>
+      <c r="E102" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>102</v>
       </c>
@@ -2141,8 +3344,14 @@
       <c r="C103" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D103" t="s">
+        <v>306</v>
+      </c>
+      <c r="E103" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>103</v>
       </c>
@@ -2152,8 +3361,14 @@
       <c r="C104" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D104" t="s">
+        <v>307</v>
+      </c>
+      <c r="E104" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>104</v>
       </c>
@@ -2163,8 +3378,14 @@
       <c r="C105" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D105" t="s">
+        <v>308</v>
+      </c>
+      <c r="E105" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>105</v>
       </c>
@@ -2174,8 +3395,14 @@
       <c r="C106" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D106" t="s">
+        <v>309</v>
+      </c>
+      <c r="E106" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>106</v>
       </c>
@@ -2185,8 +3412,14 @@
       <c r="C107" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D107" t="s">
+        <v>310</v>
+      </c>
+      <c r="E107" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>107</v>
       </c>
@@ -2196,8 +3429,14 @@
       <c r="C108" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D108" t="s">
+        <v>311</v>
+      </c>
+      <c r="E108" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>108</v>
       </c>
@@ -2207,8 +3446,14 @@
       <c r="C109" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D109" t="s">
+        <v>312</v>
+      </c>
+      <c r="E109" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>109</v>
       </c>
@@ -2218,8 +3463,14 @@
       <c r="C110" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D110" t="s">
+        <v>313</v>
+      </c>
+      <c r="E110" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>110</v>
       </c>
@@ -2229,8 +3480,14 @@
       <c r="C111" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D111" t="s">
+        <v>314</v>
+      </c>
+      <c r="E111" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>111</v>
       </c>
@@ -2240,8 +3497,14 @@
       <c r="C112" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D112" t="s">
+        <v>315</v>
+      </c>
+      <c r="E112" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>112</v>
       </c>
@@ -2251,8 +3514,14 @@
       <c r="C113" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D113" t="s">
+        <v>316</v>
+      </c>
+      <c r="E113" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>113</v>
       </c>
@@ -2262,8 +3531,14 @@
       <c r="C114" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D114" t="s">
+        <v>317</v>
+      </c>
+      <c r="E114" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>114</v>
       </c>
@@ -2273,8 +3548,14 @@
       <c r="C115" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D115" t="s">
+        <v>318</v>
+      </c>
+      <c r="E115" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>115</v>
       </c>
@@ -2284,8 +3565,14 @@
       <c r="C116" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D116" t="s">
+        <v>319</v>
+      </c>
+      <c r="E116" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>116</v>
       </c>
@@ -2295,8 +3582,14 @@
       <c r="C117" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D117" t="s">
+        <v>320</v>
+      </c>
+      <c r="E117" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>117</v>
       </c>
@@ -2306,8 +3599,14 @@
       <c r="C118" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D118" t="s">
+        <v>321</v>
+      </c>
+      <c r="E118" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>118</v>
       </c>
@@ -2317,8 +3616,14 @@
       <c r="C119" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D119" t="s">
+        <v>322</v>
+      </c>
+      <c r="E119" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>119</v>
       </c>
@@ -2328,8 +3633,14 @@
       <c r="C120" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D120" t="s">
+        <v>323</v>
+      </c>
+      <c r="E120" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>120</v>
       </c>
@@ -2339,8 +3650,14 @@
       <c r="C121" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D121" t="s">
+        <v>324</v>
+      </c>
+      <c r="E121" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>121</v>
       </c>
@@ -2350,8 +3667,14 @@
       <c r="C122" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D122" t="s">
+        <v>325</v>
+      </c>
+      <c r="E122" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <v>122</v>
       </c>
@@ -2361,8 +3684,14 @@
       <c r="C123" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D123" t="s">
+        <v>326</v>
+      </c>
+      <c r="E123" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>123</v>
       </c>
@@ -2372,8 +3701,14 @@
       <c r="C124" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D124" t="s">
+        <v>327</v>
+      </c>
+      <c r="E124" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <v>124</v>
       </c>
@@ -2383,8 +3718,14 @@
       <c r="C125" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D125" t="s">
+        <v>328</v>
+      </c>
+      <c r="E125" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>125</v>
       </c>
@@ -2394,8 +3735,14 @@
       <c r="C126" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D126" t="s">
+        <v>329</v>
+      </c>
+      <c r="E126" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>126</v>
       </c>
@@ -2405,8 +3752,14 @@
       <c r="C127" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D127" t="s">
+        <v>330</v>
+      </c>
+      <c r="E127" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>127</v>
       </c>
@@ -2416,8 +3769,14 @@
       <c r="C128" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D128" t="s">
+        <v>331</v>
+      </c>
+      <c r="E128" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <v>128</v>
       </c>
@@ -2427,8 +3786,14 @@
       <c r="C129" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D129" t="s">
+        <v>332</v>
+      </c>
+      <c r="E129" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <v>129</v>
       </c>
@@ -2438,8 +3803,14 @@
       <c r="C130" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D130" t="s">
+        <v>333</v>
+      </c>
+      <c r="E130" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <v>130</v>
       </c>
@@ -2449,8 +3820,14 @@
       <c r="C131" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D131" t="s">
+        <v>334</v>
+      </c>
+      <c r="E131" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
         <v>131</v>
       </c>
@@ -2460,8 +3837,14 @@
       <c r="C132" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D132" t="s">
+        <v>335</v>
+      </c>
+      <c r="E132" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <v>132</v>
       </c>
@@ -2471,8 +3854,14 @@
       <c r="C133" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D133" t="s">
+        <v>336</v>
+      </c>
+      <c r="E133" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <v>133</v>
       </c>
@@ -2482,8 +3871,14 @@
       <c r="C134" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D134" t="s">
+        <v>337</v>
+      </c>
+      <c r="E134" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <v>134</v>
       </c>
@@ -2493,8 +3888,14 @@
       <c r="C135" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D135" t="s">
+        <v>338</v>
+      </c>
+      <c r="E135" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <v>135</v>
       </c>
@@ -2504,8 +3905,14 @@
       <c r="C136" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D136" t="s">
+        <v>339</v>
+      </c>
+      <c r="E136" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
         <v>136</v>
       </c>
@@ -2515,8 +3922,14 @@
       <c r="C137" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D137" t="s">
+        <v>340</v>
+      </c>
+      <c r="E137" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>137</v>
       </c>
@@ -2526,8 +3939,14 @@
       <c r="C138" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D138" t="s">
+        <v>341</v>
+      </c>
+      <c r="E138" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
         <v>138</v>
       </c>
@@ -2537,8 +3956,14 @@
       <c r="C139" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D139" t="s">
+        <v>342</v>
+      </c>
+      <c r="E139" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
         <v>139</v>
       </c>
@@ -2548,8 +3973,14 @@
       <c r="C140" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D140" t="s">
+        <v>343</v>
+      </c>
+      <c r="E140" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
         <v>140</v>
       </c>
@@ -2559,8 +3990,14 @@
       <c r="C141" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D141" t="s">
+        <v>344</v>
+      </c>
+      <c r="E141" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
         <v>141</v>
       </c>
@@ -2570,8 +4007,14 @@
       <c r="C142" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D142" t="s">
+        <v>345</v>
+      </c>
+      <c r="E142" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
         <v>142</v>
       </c>
@@ -2581,8 +4024,14 @@
       <c r="C143" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D143" t="s">
+        <v>346</v>
+      </c>
+      <c r="E143" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
         <v>143</v>
       </c>
@@ -2592,8 +4041,14 @@
       <c r="C144" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D144" t="s">
+        <v>347</v>
+      </c>
+      <c r="E144" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
         <v>144</v>
       </c>
@@ -2603,8 +4058,14 @@
       <c r="C145" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D145" t="s">
+        <v>348</v>
+      </c>
+      <c r="E145" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
         <v>145</v>
       </c>
@@ -2614,8 +4075,14 @@
       <c r="C146" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D146" t="s">
+        <v>349</v>
+      </c>
+      <c r="E146" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
         <v>146</v>
       </c>
@@ -2625,8 +4092,14 @@
       <c r="C147" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D147" t="s">
+        <v>350</v>
+      </c>
+      <c r="E147" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
         <v>147</v>
       </c>
@@ -2636,8 +4109,14 @@
       <c r="C148" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D148" t="s">
+        <v>351</v>
+      </c>
+      <c r="E148" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
         <v>148</v>
       </c>
@@ -2647,8 +4126,14 @@
       <c r="C149" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D149" t="s">
+        <v>352</v>
+      </c>
+      <c r="E149" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
         <v>149</v>
       </c>
@@ -2658,8 +4143,14 @@
       <c r="C150" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D150" t="s">
+        <v>353</v>
+      </c>
+      <c r="E150" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
         <v>150</v>
       </c>
@@ -2669,8 +4160,14 @@
       <c r="C151" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D151" t="s">
+        <v>354</v>
+      </c>
+      <c r="E151" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
         <v>151</v>
       </c>
@@ -2680,8 +4177,14 @@
       <c r="C152" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D152" t="s">
+        <v>355</v>
+      </c>
+      <c r="E152" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
         <v>152</v>
       </c>
@@ -2691,8 +4194,14 @@
       <c r="C153" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D153" t="s">
+        <v>356</v>
+      </c>
+      <c r="E153" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
         <v>153</v>
       </c>
@@ -2702,8 +4211,14 @@
       <c r="C154" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D154" t="s">
+        <v>357</v>
+      </c>
+      <c r="E154" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
         <v>154</v>
       </c>
@@ -2713,8 +4228,14 @@
       <c r="C155" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D155" t="s">
+        <v>358</v>
+      </c>
+      <c r="E155" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
         <v>155</v>
       </c>
@@ -2724,8 +4245,14 @@
       <c r="C156" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D156" t="s">
+        <v>359</v>
+      </c>
+      <c r="E156" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
         <v>156</v>
       </c>
@@ -2735,8 +4262,14 @@
       <c r="C157" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D157" t="s">
+        <v>360</v>
+      </c>
+      <c r="E157" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
         <v>157</v>
       </c>
@@ -2746,8 +4279,14 @@
       <c r="C158" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D158" t="s">
+        <v>361</v>
+      </c>
+      <c r="E158" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
         <v>158</v>
       </c>
@@ -2757,8 +4296,14 @@
       <c r="C159" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D159" t="s">
+        <v>362</v>
+      </c>
+      <c r="E159" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
         <v>159</v>
       </c>
@@ -2768,8 +4313,14 @@
       <c r="C160" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D160" t="s">
+        <v>363</v>
+      </c>
+      <c r="E160" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
         <v>160</v>
       </c>
@@ -2779,8 +4330,14 @@
       <c r="C161" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D161" t="s">
+        <v>364</v>
+      </c>
+      <c r="E161" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
         <v>161</v>
       </c>
@@ -2790,8 +4347,14 @@
       <c r="C162" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D162" t="s">
+        <v>365</v>
+      </c>
+      <c r="E162" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
         <v>162</v>
       </c>
@@ -2801,8 +4364,14 @@
       <c r="C163" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D163" t="s">
+        <v>366</v>
+      </c>
+      <c r="E163" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
         <v>163</v>
       </c>
@@ -2812,8 +4381,14 @@
       <c r="C164" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D164" t="s">
+        <v>367</v>
+      </c>
+      <c r="E164" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
         <v>164</v>
       </c>
@@ -2823,8 +4398,14 @@
       <c r="C165" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D165" t="s">
+        <v>368</v>
+      </c>
+      <c r="E165" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
         <v>165</v>
       </c>
@@ -2834,8 +4415,14 @@
       <c r="C166" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D166" t="s">
+        <v>369</v>
+      </c>
+      <c r="E166" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
         <v>166</v>
       </c>
@@ -2845,8 +4432,14 @@
       <c r="C167" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D167" t="s">
+        <v>370</v>
+      </c>
+      <c r="E167" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" s="1">
         <v>167</v>
       </c>
@@ -2856,8 +4449,14 @@
       <c r="C168" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D168" t="s">
+        <v>371</v>
+      </c>
+      <c r="E168" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" s="1">
         <v>168</v>
       </c>
@@ -2867,8 +4466,14 @@
       <c r="C169" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D169" t="s">
+        <v>372</v>
+      </c>
+      <c r="E169" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
         <v>169</v>
       </c>
@@ -2878,8 +4483,14 @@
       <c r="C170" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D170" t="s">
+        <v>373</v>
+      </c>
+      <c r="E170" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
         <v>170</v>
       </c>
@@ -2889,8 +4500,14 @@
       <c r="C171" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D171" t="s">
+        <v>374</v>
+      </c>
+      <c r="E171" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
         <v>171</v>
       </c>
@@ -2900,8 +4517,14 @@
       <c r="C172" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D172" t="s">
+        <v>375</v>
+      </c>
+      <c r="E172" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" s="1">
         <v>172</v>
       </c>
@@ -2911,8 +4534,14 @@
       <c r="C173" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D173" t="s">
+        <v>376</v>
+      </c>
+      <c r="E173" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" s="1">
         <v>173</v>
       </c>
@@ -2922,8 +4551,14 @@
       <c r="C174" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D174" t="s">
+        <v>360</v>
+      </c>
+      <c r="E174" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" s="1">
         <v>174</v>
       </c>
@@ -2933,8 +4568,14 @@
       <c r="C175" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D175" t="s">
+        <v>377</v>
+      </c>
+      <c r="E175" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" s="1">
         <v>175</v>
       </c>
@@ -2944,8 +4585,14 @@
       <c r="C176" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D176" t="s">
+        <v>378</v>
+      </c>
+      <c r="E176" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" s="1">
         <v>176</v>
       </c>
@@ -2955,8 +4602,14 @@
       <c r="C177" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D177" t="s">
+        <v>379</v>
+      </c>
+      <c r="E177" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" s="1">
         <v>177</v>
       </c>
@@ -2966,8 +4619,14 @@
       <c r="C178" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D178" t="s">
+        <v>380</v>
+      </c>
+      <c r="E178" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" s="1">
         <v>178</v>
       </c>
@@ -2977,8 +4636,14 @@
       <c r="C179" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D179" t="s">
+        <v>381</v>
+      </c>
+      <c r="E179" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" s="1">
         <v>179</v>
       </c>
@@ -2988,8 +4653,14 @@
       <c r="C180" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D180" t="s">
+        <v>382</v>
+      </c>
+      <c r="E180" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" s="1">
         <v>180</v>
       </c>
@@ -2999,8 +4670,14 @@
       <c r="C181" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D181" t="s">
+        <v>383</v>
+      </c>
+      <c r="E181" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" s="1">
         <v>181</v>
       </c>
@@ -3010,8 +4687,14 @@
       <c r="C182" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D182" t="s">
+        <v>384</v>
+      </c>
+      <c r="E182" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" s="1">
         <v>182</v>
       </c>
@@ -3021,8 +4704,14 @@
       <c r="C183" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D183" t="s">
+        <v>385</v>
+      </c>
+      <c r="E183" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" s="1">
         <v>183</v>
       </c>
@@ -3032,8 +4721,14 @@
       <c r="C184" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D184" t="s">
+        <v>386</v>
+      </c>
+      <c r="E184" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" s="1">
         <v>184</v>
       </c>
@@ -3043,8 +4738,14 @@
       <c r="C185" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D185" t="s">
+        <v>387</v>
+      </c>
+      <c r="E185" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" s="1">
         <v>185</v>
       </c>
@@ -3054,8 +4755,14 @@
       <c r="C186" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D186" t="s">
+        <v>388</v>
+      </c>
+      <c r="E186" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" s="1">
         <v>186</v>
       </c>
@@ -3065,8 +4772,14 @@
       <c r="C187" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D187" t="s">
+        <v>389</v>
+      </c>
+      <c r="E187" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" s="1">
         <v>187</v>
       </c>
@@ -3076,8 +4789,14 @@
       <c r="C188" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D188" t="s">
+        <v>390</v>
+      </c>
+      <c r="E188" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" s="1">
         <v>188</v>
       </c>
@@ -3087,8 +4806,14 @@
       <c r="C189" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D189" t="s">
+        <v>391</v>
+      </c>
+      <c r="E189" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" s="1">
         <v>189</v>
       </c>
@@ -3098,8 +4823,14 @@
       <c r="C190" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D190" t="s">
+        <v>392</v>
+      </c>
+      <c r="E190" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" s="1">
         <v>190</v>
       </c>
@@ -3109,8 +4840,14 @@
       <c r="C191" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D191" t="s">
+        <v>393</v>
+      </c>
+      <c r="E191" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" s="1">
         <v>191</v>
       </c>
@@ -3120,8 +4857,14 @@
       <c r="C192" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D192" t="s">
+        <v>394</v>
+      </c>
+      <c r="E192" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" s="1">
         <v>192</v>
       </c>
@@ -3131,8 +4874,14 @@
       <c r="C193" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D193" t="s">
+        <v>395</v>
+      </c>
+      <c r="E193" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" s="1">
         <v>193</v>
       </c>
@@ -3142,8 +4891,14 @@
       <c r="C194" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D194" t="s">
+        <v>396</v>
+      </c>
+      <c r="E194" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" s="1">
         <v>194</v>
       </c>
@@ -3153,8 +4908,14 @@
       <c r="C195" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D195" t="s">
+        <v>397</v>
+      </c>
+      <c r="E195" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" s="1">
         <v>195</v>
       </c>
@@ -3164,8 +4925,14 @@
       <c r="C196" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D196" t="s">
+        <v>398</v>
+      </c>
+      <c r="E196" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" s="1">
         <v>196</v>
       </c>
@@ -3175,8 +4942,14 @@
       <c r="C197" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D197" t="s">
+        <v>399</v>
+      </c>
+      <c r="E197" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" s="1">
         <v>197</v>
       </c>
@@ -3186,8 +4959,14 @@
       <c r="C198" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D198" t="s">
+        <v>400</v>
+      </c>
+      <c r="E198" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199" s="1">
         <v>198</v>
       </c>
@@ -3197,8 +4976,14 @@
       <c r="C199" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D199" t="s">
+        <v>401</v>
+      </c>
+      <c r="E199" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" s="1">
         <v>199</v>
       </c>
@@ -3208,8 +4993,14 @@
       <c r="C200" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D200" t="s">
+        <v>402</v>
+      </c>
+      <c r="E200" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201" s="1">
         <v>200</v>
       </c>
@@ -3218,6 +5009,12 @@
       </c>
       <c r="C201" s="1" t="b">
         <v>1</v>
+      </c>
+      <c r="D201" t="s">
+        <v>403</v>
+      </c>
+      <c r="E201" s="1">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
